--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,783 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115108429</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N Hässleby  (N Hässleby ), Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>513821</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6579247</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115108303</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N Hässleby  (N Hässleby ), Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>513819</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6579243</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115108042</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hässleby (Hässleby), Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>513825</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6579277</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115107684</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hässleby (Hässleby), Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>513815</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6579300</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115107960</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hässleby (Hässleby), Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>513826</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6579277</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115108101</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>N Hässleby  (N Hässleby ), Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>513786</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6579248</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115108198</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97558</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>N Hässleby  (N Hässleby ), Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>513804</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6579265</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1568,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118741942</v>
+        <v>118741301</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvinnersta, Örebro (Kvinnersta, Örebro), Nrk</t>
+          <t>N Hässleby  (N Hässleby ), Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513840</v>
+        <v>513801</v>
       </c>
       <c r="R10" t="n">
-        <v>6579243</v>
+        <v>6579275</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>En blommande</t>
+          <t>Sex blommande ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,7 +1694,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118741301</v>
+        <v>118741942</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Hässleby  (N Hässleby ), Nrk</t>
+          <t>Kvinnersta, Örebro (Kvinnersta, Örebro), Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513801</v>
+        <v>513840</v>
       </c>
       <c r="R11" t="n">
-        <v>6579275</v>
+        <v>6579243</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sex blommande ex</t>
+          <t>En blommande</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118741301</v>
+        <v>118741942</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Hässleby  (N Hässleby ), Nrk</t>
+          <t>Kvinnersta, Örebro (Kvinnersta, Örebro), Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513801</v>
+        <v>513840</v>
       </c>
       <c r="R10" t="n">
-        <v>6579275</v>
+        <v>6579243</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sex blommande ex</t>
+          <t>En blommande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118741942</v>
+        <v>118741301</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvinnersta, Örebro (Kvinnersta, Örebro), Nrk</t>
+          <t>N Hässleby  (N Hässleby ), Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513840</v>
+        <v>513801</v>
       </c>
       <c r="R11" t="n">
-        <v>6579243</v>
+        <v>6579275</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>En blommande</t>
+          <t>Sex blommande ex</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1568,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118741942</v>
+        <v>118741301</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvinnersta, Örebro (Kvinnersta, Örebro), Nrk</t>
+          <t>N Hässleby  (N Hässleby ), Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513840</v>
+        <v>513801</v>
       </c>
       <c r="R10" t="n">
-        <v>6579243</v>
+        <v>6579275</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>En blommande</t>
+          <t>Sex blommande ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,7 +1694,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118741301</v>
+        <v>118741942</v>
       </c>
       <c r="B11" t="n">
         <v>97853</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Hässleby  (N Hässleby ), Nrk</t>
+          <t>Kvinnersta, Örebro (Kvinnersta, Örebro), Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513801</v>
+        <v>513840</v>
       </c>
       <c r="R11" t="n">
-        <v>6579275</v>
+        <v>6579243</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sex blommande ex</t>
+          <t>En blommande</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>121343291</v>
       </c>
       <c r="B12" t="n">
-        <v>90973</v>
+        <v>90983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>121343279</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343291</v>
+        <v>121343279</v>
       </c>
       <c r="B12" t="n">
-        <v>90983</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,46 +1836,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513810</v>
+        <v>513807</v>
       </c>
       <c r="R12" t="n">
-        <v>6579150</v>
+        <v>6579146</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121343279</v>
+        <v>121343291</v>
       </c>
       <c r="B13" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,37 +1938,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513807</v>
+        <v>513810</v>
       </c>
       <c r="R13" t="n">
-        <v>6579146</v>
+        <v>6579150</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343279</v>
+        <v>121343291</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>90995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,37 +1836,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513807</v>
+        <v>513810</v>
       </c>
       <c r="R12" t="n">
-        <v>6579146</v>
+        <v>6579150</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121343291</v>
+        <v>121343279</v>
       </c>
       <c r="B13" t="n">
-        <v>90983</v>
+        <v>90709</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,46 +1947,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513810</v>
+        <v>513807</v>
       </c>
       <c r="R13" t="n">
-        <v>6579150</v>
+        <v>6579146</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>121343291</v>
       </c>
       <c r="B12" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>121343279</v>
       </c>
       <c r="B13" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>121343291</v>
       </c>
       <c r="B12" t="n">
-        <v>90996</v>
+        <v>90999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>121343279</v>
       </c>
       <c r="B13" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343291</v>
+        <v>121343279</v>
       </c>
       <c r="B12" t="n">
-        <v>90999</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,46 +1836,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513810</v>
+        <v>513807</v>
       </c>
       <c r="R12" t="n">
-        <v>6579150</v>
+        <v>6579146</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121343279</v>
+        <v>121343291</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>90999</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,37 +1938,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513807</v>
+        <v>513810</v>
       </c>
       <c r="R13" t="n">
-        <v>6579146</v>
+        <v>6579150</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343279</v>
+        <v>121343291</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>91005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,37 +1836,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513807</v>
+        <v>513810</v>
       </c>
       <c r="R12" t="n">
-        <v>6579146</v>
+        <v>6579150</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121343291</v>
+        <v>121343279</v>
       </c>
       <c r="B13" t="n">
-        <v>90999</v>
+        <v>90719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,46 +1947,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513810</v>
+        <v>513807</v>
       </c>
       <c r="R13" t="n">
-        <v>6579150</v>
+        <v>6579146</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343291</v>
+        <v>121343279</v>
       </c>
       <c r="B12" t="n">
-        <v>91005</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,46 +1836,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513810</v>
+        <v>513807</v>
       </c>
       <c r="R12" t="n">
-        <v>6579150</v>
+        <v>6579146</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121343279</v>
+        <v>121343291</v>
       </c>
       <c r="B13" t="n">
-        <v>90719</v>
+        <v>91006</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,37 +1938,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513807</v>
+        <v>513810</v>
       </c>
       <c r="R13" t="n">
-        <v>6579146</v>
+        <v>6579150</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121343279</v>
+        <v>121343291</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,37 +1836,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513807</v>
+        <v>513810</v>
       </c>
       <c r="R12" t="n">
-        <v>6579146</v>
+        <v>6579150</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121343291</v>
+        <v>121343279</v>
       </c>
       <c r="B13" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,46 +1947,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hässleby, Hässleby, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513810</v>
+        <v>513807</v>
       </c>
       <c r="R13" t="n">
-        <v>6579150</v>
+        <v>6579146</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 4761-2020 artfynd.xlsx
+++ b/artfynd/A 4761-2020 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>121343291</v>
       </c>
       <c r="B12" t="n">
-        <v>91006</v>
+        <v>91014</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>121343279</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
